--- a/examples/fixtures/xlsx/basic.xlsx
+++ b/examples/fixtures/xlsx/basic.xlsx
@@ -4,6 +4,7 @@
   <sheets>
     <sheet name="Ledger" sheetId="1" r:id="rId1"/>
     <sheet name="Notes &amp; Refs" sheetId="2" r:id="rId2"/>
+    <sheet name="Formulas" sheetId="3" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -116,4 +117,139 @@
     </row>
   </sheetData>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1">
+        <v>10</v>
+      </c>
+      <c r="B1">
+        <f>A1+A2*A3</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <f>(A1+A2)*A3</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>2.5</v>
+      </c>
+      <c r="B3">
+        <f>A1/A2</f>
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B4" t="e">
+        <f>A1/0</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5">
+        <f>2^10</f>
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6">
+        <f>-A2+1</f>
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7">
+        <f>50%*A1</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="str">
+        <f>"x"&amp;A1</f>
+        <v>x10</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="b">
+        <f>A1&gt;A2</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="str">
+        <f>IF(A1&gt;A2,"big","small")</f>
+        <v>big</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11">
+        <f>ROUND(A3,0)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12">
+        <f>SUM(A1:A3)</f>
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13">
+        <f>AVERAGE(A1:A3)</f>
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14">
+        <f>MIN(A1:A3)</f>
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15">
+        <f>MAX(A1:A3)</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16">
+        <f>COUNT(A1:A4)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="str">
+        <f>IFERROR(A1/0,"caught")</f>
+        <v>caught</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18">
+        <f>NOW()</f>
+        <v>45870.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19">
+        <f>XLOOKUP(A1,A1:A3,A1:A3)</f>
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>
--- a/examples/fixtures/xlsx/basic.xlsx
+++ b/examples/fixtures/xlsx/basic.xlsx
@@ -5,6 +5,7 @@
     <sheet name="Ledger" sheetId="1" r:id="rId1"/>
     <sheet name="Notes &amp; Refs" sheetId="2" r:id="rId2"/>
     <sheet name="Formulas" sheetId="3" r:id="rId5"/>
+    <sheet name="Circular" sheetId="4" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
@@ -252,4 +253,30 @@
     </row>
   </sheetData>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1">
+        <f>B1+1</f>
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <f>A1+1</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>5</v>
+      </c>
+      <c r="B2">
+        <f>A2*3</f>
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>
--- a/examples/fixtures/xlsx/basic.xlsx
+++ b/examples/fixtures/xlsx/basic.xlsx
@@ -247,7 +247,7 @@
     </row>
     <row r="19">
       <c r="B19">
-        <f>XLOOKUP(A1,A1:A3,A1:A3)</f>
+        <f>_xll.HPVAL(A1)</f>
         <v>10</v>
       </c>
     </row>
